--- a/lead_magnets/2026_外贸防泄露自动核价模板_Kelvin极客版.xlsx
+++ b/lead_magnets/2026_外贸防泄露自动核价模板_Kelvin极客版.xlsx
@@ -171,7 +171,7 @@
   </si>
   <si>
     <t xml:space="preserve">💡 技术老友 Kelvin 的心里话：
-亲爱的外贸朋友，如果你还在每天手动算几十个复杂 SKU、或者买家总发长篇英文邮件询价让你头大，试试我为你写好的免费 AI 自动审单引擎 KelvinFlow (https://kelvinflow.com)。复制邮件 10 秒全自动拆解 SKU、匹配底价并生成纯英文正式 PDF 报价单！小红书群友终身享受限时首月 ¥39 破冰特权，免审开通 7 天试用！微信: KelvinFlow (备注“小红书群友”)</t>
+亲爱的外贸朋友，如果你还在每天手动算几十个复杂 SKU、或者买家总发长篇英文邮件询价让你头大，试试我为你写好的免费 AI 自动审单引擎 KelvinFlow (https://kelvinflow.com)。复制邮件 10 秒全自动拆解 SKU、匹配底价并生成纯英文正式 PDF 报价单！小红书群友可在官方交流群内随时提需求，我来为你免审开通体验！欢迎在官方粉丝群内交流反馈</t>
   </si>
   <si>
     <t>GLOBAL EXPORT FORMAL QUOTATION</t>
